--- a/tests/fixtures/synthetic_base.xlsx
+++ b/tests/fixtures/synthetic_base.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="DATA BASE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PO record" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="客户PO" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1175,4 +1176,324 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Purchasing Document</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Purchasing Doc. Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Item Category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Purch. Doc. Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Purchasing Group</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Document Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Vendor/supplying plant</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Old Material #</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Short Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Deletion Indicator</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Order Quantity</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Order Unit</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Net price</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Price Unit</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Still to be delivered (qty)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Confirm. Category</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Delivery Date</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ship Date</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>order date</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ship to</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>final destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4500030844</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>21-44640</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CB2500.B2 Combo</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>240</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Rather Outdoors Corporation</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>E MAX SPORT PTE. LTD.</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4500030844</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00020</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21-44641</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CR3000.B2 Rod</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>120</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Rather Outdoors Corporation</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>E MAX SPORT PTE. LTD.</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4500099999</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>21-44640</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CB2500.B2 Combo</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>EMAX HQ</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>E MAX SPORT PTE. LTD.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tests/fixtures/synthetic_base.xlsx
+++ b/tests/fixtures/synthetic_base.xlsx
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:AE9"/>
+  <dimension ref="A4:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -798,62 +798,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>SHIP QTY</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2602</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2606</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2607</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2608</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2611</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2612</t>
+          <t>BALANCE QTY</t>
         </is>
       </c>
     </row>
@@ -1060,6 +1010,9 @@
       <c r="T7" t="n">
         <v>360</v>
       </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1093,7 +1046,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="H8" t="n">
         <v>28</v>
@@ -1123,8 +1076,11 @@
       <c r="S8" t="n">
         <v>24</v>
       </c>
-      <c r="V8" t="n">
+      <c r="T8" t="n">
         <v>100</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1171,6 +1127,12 @@
       </c>
       <c r="S9" t="n">
         <v>24</v>
+      </c>
+      <c r="T9" t="n">
+        <v>50</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
